--- a/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2260,6 +2260,936 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>startDownload</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>format&lt;VideoInfo.Format&gt;</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>将下载任务添加到列表并导航到下载 Tab（v2 重构）</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;startDownload:655]</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>通过ViewPager切换到下载Tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HomeFragment</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>首页Fragment，提供视频链接输入框、解析按钮、测试环境和日志反馈面板</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment:34]</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>集成Chaquopy调用Python yt-dlp，附日志面板显示运行反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化控件和事件监听器</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;onCreateView:59]</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>初始化Handler用于跨线程UI更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>initViews</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>view&lt;View&gt;</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>初始化所有界面控件，通过findViewByid获取布局中的控件实例</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;initViews:82]</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>获取输入框、按钮、日志面板等控件引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>setupListeners</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>设置按钮点击事件监听器：解析按钮调yt-dlp，测试按钮检测环境</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;setupListeners:103]</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>后台线程调用Python，避免阻塞UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>callPythonFunction</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>functionName&lt;String&gt;, parameter&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>调用Python桥接模块的指定函数，通过Chaquopy API执行Python代码</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;callPythonFunction:167]</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>首次调用时自动初始化Chaquopy Python环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>appendLog</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>text&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>向日志面板追加一条文本，通过Handler切换到主线程更新UI</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;appendLog:215]</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>支持从后台线程调用，自动滚动到底部</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>showToast</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>message&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>显示简短的Toast提示消息</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;showToast:252]</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>封装Toast.makeText调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HomeFragment</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>首页Fragment，提供视频链接输入框、解析按钮、测试环境和日志反馈面板</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment:34]</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>集成Chaquopy调用Python yt-dlp，附日志面板显示运行反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化控件和事件监听器</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;onCreateView:59]</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>初始化Handler用于跨线程UI更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>initViews</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>view&lt;View&gt;</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>初始化所有界面控件，通过findViewByid获取布局中的控件实例</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;initViews:82]</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>获取输入框、按钮、日志面板等控件引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>setupListeners</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>设置按钮点击事件监听器：解析按钮调yt-dlp，测试按钮检测环境</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;setupListeners:103]</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>后台线程调用Python，避免阻塞UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>callPythonFunction</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>functionName&lt;String&gt;, parameter&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>调用Python桥接模块的指定函数，通过Chaquopy API执行Python代码</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;callPythonFunction:167]</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>首次调用时自动初始化Chaquopy Python环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>appendLog</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>text&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>向日志面板追加一条文本，通过Handler切换到主线程更新UI</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;appendLog:215]</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>支持从后台线程调用，自动滚动到底部</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>showToast</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>message&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>显示简短的Toast提示消息</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;showToast:252]</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>封装Toast.makeText调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HomeFragment</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>首页Fragment，提供视频链接输入框、解析按钮、测试环境和日志反馈面板</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment:34]</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>集成Chaquopy调用Python yt-dlp，附日志面板显示运行反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化控件和事件监听器</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;onCreateView:59]</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>初始化Handler用于跨线程UI更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>initViews</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>view&lt;View&gt;</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>初始化所有界面控件，通过findViewByid获取布局中的控件实例</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;initViews:82]</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>获取输入框、按钮、日志面板等控件引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>setupListeners</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>设置按钮点击事件监听器：解析按钮调yt-dlp，测试按钮检测环境</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;setupListeners:103]</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>后台线程调用Python，避免阻塞UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>callPythonFunction</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>functionName&lt;String&gt;, parameter&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>调用Python桥接模块的指定函数，通过Chaquopy API执行Python代码</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;callPythonFunction:167]</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>首次调用时自动初始化Chaquopy Python环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>appendLog</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>text&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>向日志面板追加一条文本，通过Handler切换到主线程更新UI</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;appendLog:215]</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>支持从后台线程调用，自动滚动到底部</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>showToast</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>message&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>显示简短的Toast提示消息</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;showToast:252]</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>封装Toast.makeText调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>simplifyCodec</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>vcodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>简化视频编码名称，将avc1.640028转为h264，hevc转为h265，av01转为av1</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;simplifyCodec:513]</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>用于格式行标签显示，unknown编码截取前8字符</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3190,6 +3190,330 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HomeFragment</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>首页Fragment，提供视频链接输入框、解析按钮、测试环境和日志反馈面板</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment:34]</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>集成Chaquopy调用Python yt-dlp，附日志面板显示运行反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化控件和事件监听器</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;onCreateView:59]</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>初始化Handler用于跨线程UI更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>initViews</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>view&lt;View&gt;</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>初始化所有界面控件，通过findViewByid获取布局中的控件实例</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;initViews:82]</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>获取输入框、按钮、日志面板等控件引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>setupListeners</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>设置按钮点击事件监听器：解析按钮调yt-dlp，测试按钮检测环境</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;setupListeners:103]</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>后台线程调用Python，避免阻塞UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>callPythonFunction</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>functionName&lt;String&gt;, parameter&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>调用Python桥接模块的指定函数，通过Chaquopy API执行Python代码</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;callPythonFunction:167]</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>首次调用时自动初始化Chaquopy Python环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>appendLog</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>text&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>向日志面板追加一条文本，通过Handler切换到主线程更新UI</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;appendLog:215]</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>支持从后台线程调用，自动滚动到底部</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>showToast</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>message&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>显示简短的Toast提示消息</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;showToast:252]</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>封装Toast.makeText调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>simplifyCodec</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>vcodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>简化视频编码名称，将avc1.640028转为h264，hevc转为h265，av01转为av1</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[HomeFragment-&gt;simplifyCodec:513]</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>用于格式行标签显示，unknown编码截取前8字符</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/HomeFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3514,6 +3514,216 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>onParseClick</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无（从输入框获取文本）</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>解析按钮点击处理：正则提取链接 -&gt; 检测无内置提取器平台并警告 -&gt; 重复检测 -&gt; 执行解析</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[onParseClick:205]</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:09:02</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>已重构：集成链接提取和平台检测逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>extractUrlFromInput</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>input&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>url&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>使用正则表达式从用户输入的文本中提取第一个有效链接</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[extractUrlFromInput:262]</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:09:02</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>新增功能：链接正则提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>showUnsupportedPlatformWarning</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>platformName&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>显示平台无内置提取器的浮层警告，渐显动画+6秒后渐隐消失</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[showUnsupportedPlatformWarning:291]</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:19:07</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>已优化：改为浮层样式，6秒消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>getPlatformDisplayName</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>platform&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>displayName&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>将平台标识常量转换为用户可读的中文显示名称</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[getPlatformDisplayName:315]</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:09:02</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>新增功能：平台名称映射</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>hidePlatformWarningToast</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>隐藏平台兼容性警告浮层</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/home/HomeFragment.java)[hidePlatformWarningToast:327]</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:19:07</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>新增方法</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
